--- a/esyluban/examples/dev/DataTables/test/multi_rows_record.xlsx
+++ b/esyluban/examples/dev/DataTables/test/multi_rows_record.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD51"/>
+  <dimension ref="A1:AD18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="13.6285714285714" customWidth="1" style="8" min="3" max="3"/>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>full_name="test.TbMultiRowRecord" &amp; value_type="test.MultiRowRecord" &amp; read_schema_from_file="false" &amp; input="test/multi_rows_record.xlsx" &amp; output="test_tbmultirowrecord"</t>
+          <t>full_name="test.TbMultiRowRecord" &amp; input="test/multi_rows_record.xlsx"</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
@@ -1700,39 +1700,6 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="R1:V1"/>

--- a/esyluban/examples/dev/DataTables/test/multi_rows_record.xlsx
+++ b/esyluban/examples/dev/DataTables/test/multi_rows_record.xlsx
@@ -1218,6 +1218,51 @@
           <t>名字</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1702,16 +1747,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="R1:V1"/>
-    <mergeCell ref="D5:M5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="N1:Q1"/>
-    <mergeCell ref="S2:V2"/>
-    <mergeCell ref="W1:Z1"/>
-    <mergeCell ref="AA1:AD1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="S3:V3"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="W2:Z2"/>
+    <mergeCell ref="R2:V2"/>
+    <mergeCell ref="D6:M6"/>
+    <mergeCell ref="AA2:AD2"/>
+    <mergeCell ref="N2:Q2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
